--- a/VibeProject1/Assets/Table/Tactics/RoleGroupTactics.xlsx
+++ b/VibeProject1/Assets/Table/Tactics/RoleGroupTactics.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -613,10 +613,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -627,7 +627,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -638,6 +638,17 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -803,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,7 +835,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>돌격</t>
+          <t>접근 공격</t>
         </is>
       </c>
     </row>
@@ -834,7 +845,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>방진 형성</t>
+          <t>돌격</t>
         </is>
       </c>
     </row>
@@ -844,7 +855,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>자리 사수</t>
+          <t>방진 형성</t>
         </is>
       </c>
     </row>
@@ -854,7 +865,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>포위 공격</t>
+          <t>자리 사수</t>
         </is>
       </c>
     </row>
@@ -863,6 +874,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
+        <is>
+          <t>포위 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>산개 공격</t>
         </is>
